--- a/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort. Papa dit : chat, chatte, chaton. Ce sont trois noms. Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit. Papa dit : chien, chienne, chiot. Ce sont trois noms de la famille. Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+          <t>Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort. Chat, chatte, chaton. Ce sont trois noms. Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit. Chien, chienne, chiot. Ce sont trois noms de la famille. Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort.
+papa|Chat, chatte, chaton. Ce sont trois noms.
+narrateur|Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit.
+papa|Chien, chienne, chiot. Ce sont trois noms de la famille.
+narrateur|Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël a dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël caresse l'herbe. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,11 @@
           <t>narrateur|Yaël a dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1847,7 @@
           <t>narrateur|Yaël caresse l'herbe. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yaël dit les trois noms au jardin</t>
+          <t>L'escargot après la pluie</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut trouver l'escargot après la pluie. Elle voit une poule, puis un chat. L'escargot brille sur une feuille. Nina le salue, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort. Chat, chatte, chaton. Ce sont trois noms. Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit. Chien, chienne, chiot. Ce sont trois noms de la famille. Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+          <t>Une goutte quitte encore la gouttière. Elle tombe dans une flaque ronde. Le jardin sent la terre mouillée. Les laitues brillent, toutes vertes. Nina vit ici, avec papa. Ses bottes jaunes font un bruit mou. Papa, je veux l'escargot. Celui de la pluie ? Oui. Il laisse un fil d'argent. En ce moment, Nina prend la main de papa. L'herbe est froide, un peu haute. Une poule mouillée picore près du bac. Une poule ! Oui, Nina. Elle cherche des vers. Nina la regarde, puis avance. Un chat gris se lèche sur le muret. Un chat ! Il n'aime pas l'eau. Nina cherche le fil d'argent. Les feuilles sont trop brillantes. Je ne le vois pas. On regarde la laitue ? Papa soulève une grande feuille. Nina regarde dessous. Rien, sauf une goutte. Encore. Sous la deuxième feuille, un point brun. Une coquille luisante avance très lentement. L'escargot ! Poule, chat, escargot. Tu les as vus. Le petit de la poule, c'est le poussin. Trois noms de la famille. Nina s'accroupit près de la feuille. Bonjour, tout doux. L'escargot sort deux cornes minuscules. Il te salue, Nina. Merci d'avoir cherché sans le prendre. Il brille. Nina suit le fil d'argent des yeux. Il va d'une nervure à l'autre. Il va tout seul. Oui. Sans qu'on le porte. La poule secoue une goutte de l'aile. Le chat se lèche encore, plus loin. Ils ne le voient pas. Toi, tu l'as trouvé. Nina pose un doigt à côté, pas dessus. Tu restes tout doux ? Oui, papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort. Papa dit : chat, chatte, chaton. Ce sont &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit. Papa dit : chien, chienne, chiot. Ce sont trois noms de la famille. Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte quitte encore la gouttière. Elle tombe dans une flaque ronde. Le jardin sent la terre mouillée. Les laitues brillent, toutes vertes. Nina vit ici, avec papa. Ses bottes jaunes font un bruit mou. Papa, je veux l'escargot. Celui de la pluie ? Oui. Il laisse un fil d'argent. En ce moment, Nina prend la main de papa. L'herbe est froide, un peu haute. Une poule mouillée picore près du bac. Une poule ! Oui, Nina. Elle cherche des vers. Nina la regarde, puis avance. Un chat gris se lèche sur le muret. Un chat ! Il n'aime pas l'eau. Nina cherche le fil d'argent. Les feuilles sont trop brillantes. Je ne le vois pas. On regarde la laitue ? Papa soulève une grande feuille. Nina regarde dessous. Rien, sauf une goutte. Encore. Sous la deuxième feuille, un point brun. Une coquille luisante avance très lentement. L'escargot ! Poule, chat, escargot. Tu les as vus. Le petit de la poule, c'est le poussin. Trois noms de la famille. Nina s'accroupit près de la feuille. Bonjour, tout doux. L'escargot sort deux cornes minuscules. Il te salue, Nina. Merci d'avoir cherché sans le prendre. Il brille. Nina suit le fil d'argent des yeux. Il va d'une nervure à l'autre. Il va tout seul. Oui. Sans qu'on le porte. La poule secoue une goutte de l'aile. Le chat se lèche encore, plus loin. Ils ne le voient pas. Toi, tu l'as trouvé. Nina pose un doigt à côté, pas dessus. Tu restes tout doux ? Oui, papa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yaël est au jardin avec papa. Un chat miaule. Une chatte se lèche. Un chaton dort.
-papa|Chat, chatte, chaton. Ce sont trois noms.
-narrateur|Yaël répète. Plus loin, un chien aboie. Une chienne marche. Un chiot suit.
-papa|Chien, chienne, chiot. Ce sont trois noms de la famille.
-narrateur|Yaël dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+          <t>narrateur|Une goutte quitte encore la gouttière.
+narrateur|Elle tombe dans une flaque ronde.
+narrateur|Le jardin sent la terre mouillée.
+narrateur|Les laitues brillent, toutes vertes.
+narrateur|Nina vit ici, avec papa.
+narrateur|Ses bottes jaunes font un bruit mou.
+enfant-f|Papa, je veux l'escargot.
+papa|Celui de la pluie ?
+enfant-f|Oui.
+enfant-f|Il laisse un fil d'argent.
+narrateur|En ce moment, Nina prend la main de papa.
+narrateur|L'herbe est froide, un peu haute.
+narrateur|Une poule mouillée picore près du bac.
+enfant-f|Une poule !
+papa|Oui, Nina.
+papa|Elle cherche des vers.
+narrateur|Nina la regarde, puis avance.
+narrateur|Un chat gris se lèche sur le muret.
+enfant-f|Un chat !
+papa|Il n'aime pas l'eau.
+narrateur|Nina cherche le fil d'argent.
+narrateur|Les feuilles sont trop brillantes.
+enfant-f|Je ne le vois pas.
+papa|On regarde la laitue ?
+narrateur|Papa soulève une grande feuille.
+narrateur|Nina regarde dessous.
+narrateur|Rien, sauf une goutte.
+enfant-f|Encore.
+narrateur|Sous la deuxième feuille, un point brun.
+narrateur|Une coquille luisante avance très lentement.
+enfant-f|L'escargot !
+papa|Poule, chat, escargot.
+papa|Tu les as vus.
+papa|Le petit de la poule, c'est le poussin.
+papa|Trois noms de la famille.
+narrateur|Nina s'accroupit près de la feuille.
+enfant-f|Bonjour, tout doux.
+narrateur|L'escargot sort deux cornes minuscules.
+papa|Il te salue, Nina.
+papa|Merci d'avoir cherché sans le prendre.
+enfant-f|Il brille.
+narrateur|Nina suit le fil d'argent des yeux.
+narrateur|Il va d'une nervure à l'autre.
+enfant-f|Il va tout seul.
+papa|Oui.
+papa|Sans qu'on le porte.
+narrateur|La poule secoue une goutte de l'aile.
+narrateur|Le chat se lèche encore, plus loin.
+enfant-f|Ils ne le voient pas.
+papa|Toi, tu l'as trouvé.
+narrateur|Nina pose un doigt à côté, pas dessus.
+papa|Tu restes tout doux ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1408,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le chat, la chatte, et le petit. Quel est le petit ?</t>
+          <t>Après la pluie, qui Nina cherche-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chat, la chatte, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après la pluie, qui Nina cherche-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1423,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>chaton</t>
+          <t>escargot</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>chaton | le chaton | petit | le petit</t>
+          <t>escargot | le escargot | un escargot</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1443,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le petit du chat et de la chatte. Qui est-ce ?</t>
+          <t>C'est l'escargot. Qui Nina cherche-t-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1492,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1564,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chat, la chatte, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après la pluie, qui Nina cherche-t-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yaël a dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+          <t>L'escargot avance sur la nervure. Le fil d'argent suit derrière. Il est tout lent. Oui. On le laisse sur sa feuille. Tu as vu la poule, aussi ? Et le chat. Une goutte tombe encore, tout près. On reste regarder ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yaël a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Chat, chatte, chaton. Chien, chienne, chiot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'escargot avance sur la nervure. Le fil d'argent suit derrière. Il est tout lent. Oui. On le laisse sur sa feuille. Tu as vu la poule, aussi ? Et le chat. Une goutte tombe encore, tout près. On reste regarder ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,14 +1652,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1735,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yaël a dit les trois noms. Chat, chatte, chaton. Chien, chienne, chiot.</t>
+          <t>narrateur|L'escargot avance sur la nervure.
+narrateur|Le fil d'argent suit derrière.
+enfant-f|Il est tout lent.
+papa|Oui.
+papa|On le laisse sur sa feuille.
+papa|Tu as vu la poule, aussi ?
+enfant-f|Et le chat.
+narrateur|Une goutte tombe encore, tout près.
+papa|On reste regarder ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1708,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Yaël caresse l'herbe. Papa sourit.</t>
+          <t>Ils reculent vers la gouttière. La poule secoue une aile mouillée. Le chat bâille sur le muret. L'escargot reste. Sur sa feuille brillante. Tu lui as parlé ? Oui. Nina garde une goutte au bout du nez. La gouttière chante encore un peu. Comme l'escargot, tout lent. Les laitues restent brillantes, toutes ouvertes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yaël caresse l'herbe. Papa sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils reculent vers la gouttière. La poule secoue une aile mouillée. Le chat bâille sur le muret. L'escargot reste. Sur sa feuille brillante. Tu lui as parlé ? Oui. Nina garde une goutte au bout du nez. La gouttière chante encore un peu. Comme l'escargot, tout lent. Les laitues restent brillantes, toutes ouvertes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1837,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1912,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Yaël caresse l'herbe. Papa sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils reculent vers la gouttière.
+narrateur|La poule secoue une aile mouillée.
+narrateur|Le chat bâille sur le muret.
+enfant-f|L'escargot reste.
+papa|Sur sa feuille brillante.
+papa|Tu lui as parlé ?
+enfant-f|Oui.
+narrateur|Nina garde une goutte au bout du nez.
+papa|La gouttière chante encore un peu.
+enfant-f|Comme l'escargot, tout lent.
+narrateur|Les laitues restent brillantes, toutes ouvertes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sa coquille brille. Après la pluie. La coquille brille sur la feuille mouillée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sa coquille brille. Après la pluie. La coquille brille sur la feuille mouillée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2010,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2089,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Sa coquille brille.
+papa|Après la pluie.
+narrateur|La coquille brille sur la feuille mouillée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin après la pluie, gouttière, laitue</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yaël, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
